--- a/artfynd/A 11682-2022 artfynd.xlsx
+++ b/artfynd/A 11682-2022 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>136478486</v>
       </c>
       <c r="B3" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>136478488</v>
       </c>
       <c r="B4" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11682-2022 artfynd.xlsx
+++ b/artfynd/A 11682-2022 artfynd.xlsx
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Hammar, Hans Bucht</t>
+          <t>Hans Bucht, Karl Hammar</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Hammar, Hans Bucht</t>
+          <t>Hans Bucht, Karl Hammar</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 11682-2022 artfynd.xlsx
+++ b/artfynd/A 11682-2022 artfynd.xlsx
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Bucht, Karl Hammar</t>
+          <t>Karl Hammar, Hans Bucht</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Bucht, Karl Hammar</t>
+          <t>Karl Hammar, Hans Bucht</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
